--- a/kapremont/output/Квитанции_квартальные_Магистральная-2_цветной.xlsx
+++ b/kapremont/output/Квитанции_квартальные_Магистральная-2_цветной.xlsx
@@ -1042,7 +1042,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Ячейки на бирюзовом фоне — для ввода. Всё остальное в книге считается формулами от них; квитанции и письма пересчитаются сами.</t>
+          <t>Залитые ячейки — для ввода. Всё остальное в книге считается формулами от них; квитанции и письма пересчитаются сами.</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="30" customHeight="1">
       <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Начислено за месяц, руб.</t>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>«от Председателя … Яворсюк Елены Викторовны»</t>
+          <t>«от Председателя … Ивановой Марии Петровны»</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       <c r="F39" s="3" t="n"/>
       <c r="G39" s="3" t="n"/>
     </row>
-    <row r="40" ht="44" customHeight="1">
+    <row r="40" ht="52" customHeight="1">
       <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Получатель платежа</t>

--- a/kapremont/output/Квитанции_квартальные_Магистральная-2_цветной.xlsx
+++ b/kapremont/output/Квитанции_квартальные_Магистральная-2_цветной.xlsx
@@ -1768,7 +1768,7 @@
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="B16" s="81">
-        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$34),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$34),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$34)&amp;" и с учётом начислений по "&amp;"декабрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
+        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$34),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$34),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$34)&amp;" и с учётом начислений по "&amp;"декабрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
       <c r="C16" s="81" t="n"/>
@@ -32167,7 +32167,7 @@
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="20">
-        <f>"Специальный счёт МКД · "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14</f>
+        <f>"Специальный счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
       <c r="C3" s="21" t="n"/>
@@ -32256,7 +32256,7 @@
         </is>
       </c>
       <c r="C9" s="34">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (спец.счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;")"</f>
         <v/>
       </c>
       <c r="D9" s="34" t="n"/>
@@ -32864,7 +32864,7 @@
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="20">
-        <f>"Специальный счёт МКД · "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14</f>
+        <f>"Специальный счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
       <c r="C3" s="21" t="n"/>
@@ -32953,7 +32953,7 @@
         </is>
       </c>
       <c r="C9" s="34">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (спец.счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;")"</f>
         <v/>
       </c>
       <c r="D9" s="34" t="n"/>
@@ -33561,7 +33561,7 @@
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="20">
-        <f>"Специальный счёт МКД · "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14</f>
+        <f>"Специальный счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
       <c r="C3" s="21" t="n"/>
@@ -33650,7 +33650,7 @@
         </is>
       </c>
       <c r="C9" s="34">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (спец.счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;")"</f>
         <v/>
       </c>
       <c r="D9" s="34" t="n"/>
@@ -34258,7 +34258,7 @@
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="20">
-        <f>"Специальный счёт МКД · "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14</f>
+        <f>"Специальный счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
       <c r="C3" s="21" t="n"/>
@@ -34347,7 +34347,7 @@
         </is>
       </c>
       <c r="C9" s="34">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (спец.счет МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;")"</f>
         <v/>
       </c>
       <c r="D9" s="34" t="n"/>
@@ -35032,7 +35032,7 @@
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="B16" s="81">
-        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$31)&amp;" и с учётом начислений по "&amp;"март "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
+        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$31)&amp;" и с учётом начислений по "&amp;"март "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
       <c r="C16" s="81" t="n"/>
@@ -35273,7 +35273,7 @@
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="B16" s="81">
-        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$32)&amp;" и с учётом начислений по "&amp;"июнь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
+        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$32)&amp;" и с учётом начислений по "&amp;"июнь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
       <c r="C16" s="81" t="n"/>
@@ -35514,7 +35514,7 @@
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="B16" s="81">
-        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$33)&amp;" и с учётом начислений по "&amp;"сентябрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
+        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$33)&amp;" и с учётом начислений по "&amp;"сентябрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
       <c r="C16" s="81" t="n"/>
